--- a/data/Сопоставление MunicOffic и QGIS_name.xlsx
+++ b/data/Сопоставление MunicOffic и QGIS_name.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinamaleeva/Documents/Грант ДВ/Визуализация/project_DV/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinamaleeva/Documents/Грант ДВ/Визуализация/project_DV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC3DC06-48EB-2E41-98D7-69B387FB86A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151BE1B7-D67A-BE4C-BDF9-81F20BB78FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7100" yWindow="5720" windowWidth="26240" windowHeight="14760" xr2:uid="{A28F7CF3-09B8-0749-B5E8-1B883BAC6B48}"/>
+    <workbookView xWindow="10220" yWindow="23700" windowWidth="26240" windowHeight="14760" xr2:uid="{A28F7CF3-09B8-0749-B5E8-1B883BAC6B48}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="375">
   <si>
     <t>QGIS_name</t>
   </si>
@@ -775,9 +775,6 @@
     <t>городской округ город Белогорск</t>
   </si>
   <si>
-    <t>Белогорск</t>
-  </si>
-  <si>
     <t>Биробиджанский муниципальный район</t>
   </si>
   <si>
@@ -1154,6 +1151,15 @@
   </si>
   <si>
     <t>oktmo_name_actual</t>
+  </si>
+  <si>
+    <t>Читинский район</t>
+  </si>
+  <si>
+    <t>Спасский район</t>
+  </si>
+  <si>
+    <t>городской округ Белогорск</t>
   </si>
 </sst>
 </file>
@@ -1585,7 +1591,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1593,10 +1599,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1612,7 +1618,7 @@
         <v>235</v>
       </c>
       <c r="B4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1620,15 +1626,15 @@
         <v>236</v>
       </c>
       <c r="B5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1652,7 +1658,7 @@
         <v>238</v>
       </c>
       <c r="B9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -1668,7 +1674,7 @@
         <v>239</v>
       </c>
       <c r="B11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -1676,7 +1682,7 @@
         <v>240</v>
       </c>
       <c r="B12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -1684,12 +1690,12 @@
         <v>241</v>
       </c>
       <c r="B13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
@@ -1724,7 +1730,7 @@
         <v>242</v>
       </c>
       <c r="B18" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -1740,7 +1746,7 @@
         <v>243</v>
       </c>
       <c r="B20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -1764,7 +1770,7 @@
         <v>244</v>
       </c>
       <c r="B23" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -1793,18 +1799,18 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -1833,10 +1839,10 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B32" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -1873,18 +1879,18 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B37" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B38" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -1897,10 +1903,10 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B40" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -1940,7 +1946,7 @@
         <v>245</v>
       </c>
       <c r="B45" t="s">
-        <v>246</v>
+        <v>374</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
@@ -1953,10 +1959,10 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B47" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
@@ -2073,7 +2079,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B62" t="s">
         <v>66</v>
@@ -2081,7 +2087,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B63" t="s">
         <v>67</v>
@@ -2089,7 +2095,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B64" t="s">
         <v>68</v>
@@ -2097,7 +2103,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B65" t="s">
         <v>69</v>
@@ -2113,10 +2119,10 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B67" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
@@ -2129,7 +2135,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B69" t="s">
         <v>74</v>
@@ -2153,7 +2159,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B72" t="s">
         <v>77</v>
@@ -2193,10 +2199,10 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B77" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
@@ -2233,10 +2239,10 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B82" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
@@ -2249,10 +2255,10 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B84" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
@@ -2281,26 +2287,26 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B88" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B89" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B90" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
@@ -2313,10 +2319,10 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B92" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
@@ -2329,18 +2335,18 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B94" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B95" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
@@ -2377,10 +2383,10 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B100" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
@@ -2449,10 +2455,10 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B109" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
@@ -2489,7 +2495,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B114" t="s">
         <v>123</v>
@@ -2497,10 +2503,10 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B115" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
@@ -2521,10 +2527,10 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B118" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
@@ -2545,10 +2551,10 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B121" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
@@ -2625,10 +2631,10 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
@@ -2641,7 +2647,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B133" t="s">
         <v>148</v>
@@ -2673,15 +2679,15 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B137" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B138" t="s">
         <v>155</v>
@@ -2689,15 +2695,15 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B139" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B140" t="s">
         <v>156</v>
@@ -2705,18 +2711,18 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B141" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B142" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
@@ -2729,10 +2735,10 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B144" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
@@ -2745,10 +2751,10 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B146" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
@@ -2761,10 +2767,10 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B148" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
@@ -2777,10 +2783,10 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B150" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
@@ -2809,10 +2815,10 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B154" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
@@ -2857,26 +2863,26 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B160" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B161" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B162" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
@@ -2889,18 +2895,18 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B164" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B165" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
@@ -2913,18 +2919,18 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B167" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B168" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
@@ -2977,10 +2983,10 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B175" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
@@ -3001,10 +3007,10 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B178" t="s">
-        <v>306</v>
+        <v>373</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
@@ -3017,10 +3023,10 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B180" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
@@ -3065,26 +3071,26 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B186" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B187" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B188" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
@@ -3097,10 +3103,10 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B190" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
@@ -3121,18 +3127,18 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
+        <v>366</v>
+      </c>
+      <c r="B193" t="s">
         <v>367</v>
-      </c>
-      <c r="B193" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B194" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
@@ -3145,18 +3151,18 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B196" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B197" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
@@ -3177,10 +3183,10 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B200" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
@@ -3201,18 +3207,18 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B203" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B204" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
@@ -3233,18 +3239,18 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B207" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B208" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
@@ -3329,10 +3335,10 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B219" t="s">
-        <v>307</v>
+        <v>372</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
@@ -3345,18 +3351,18 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B221" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B222" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
@@ -3377,10 +3383,10 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B225" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
@@ -3393,18 +3399,18 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B227" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B228" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">

--- a/data/Сопоставление MunicOffic и QGIS_name.xlsx
+++ b/data/Сопоставление MunicOffic и QGIS_name.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinamaleeva/Documents/Грант ДВ/Визуализация/project_DV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151BE1B7-D67A-BE4C-BDF9-81F20BB78FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A58CE1-D485-B047-BB48-3565302FDF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10220" yWindow="23700" windowWidth="26240" windowHeight="14760" xr2:uid="{A28F7CF3-09B8-0749-B5E8-1B883BAC6B48}"/>
+    <workbookView xWindow="3520" yWindow="4380" windowWidth="26240" windowHeight="14760" xr2:uid="{A28F7CF3-09B8-0749-B5E8-1B883BAC6B48}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="374">
   <si>
     <t>QGIS_name</t>
   </si>
@@ -814,9 +814,6 @@
     <t>Иволгинский муниципальный район</t>
   </si>
   <si>
-    <t>Эгвекинот (пгт Эгвекинот) муниципальный округ</t>
-  </si>
-  <si>
     <t>Карагинский муниципальный район</t>
   </si>
   <si>
@@ -910,9 +907,6 @@
     <t>Усть-Алданский муниципальный район</t>
   </si>
   <si>
-    <t>Усть-Большерецкий муниципальный район</t>
-  </si>
-  <si>
     <t>Усть-Янский муниципальный район</t>
   </si>
   <si>
@@ -1126,9 +1120,6 @@
     <t>Калганский муниципальный округ</t>
   </si>
   <si>
-    <t>Ногликский (пгт Ноглики) муниципальный округ</t>
-  </si>
-  <si>
     <t>Ононский муниципальный округ</t>
   </si>
   <si>
@@ -1160,6 +1151,12 @@
   </si>
   <si>
     <t>городской округ Белогорск</t>
+  </si>
+  <si>
+    <t>Эгвекинот муниципальный округ</t>
+  </si>
+  <si>
+    <t>Усть-Большерецкий муниципальный округ</t>
   </si>
 </sst>
 </file>
@@ -1591,7 +1588,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1599,10 +1596,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1618,7 +1615,7 @@
         <v>235</v>
       </c>
       <c r="B4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1626,15 +1623,15 @@
         <v>236</v>
       </c>
       <c r="B5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1658,7 +1655,7 @@
         <v>238</v>
       </c>
       <c r="B9" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -1674,7 +1671,7 @@
         <v>239</v>
       </c>
       <c r="B11" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -1682,7 +1679,7 @@
         <v>240</v>
       </c>
       <c r="B12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -1690,12 +1687,12 @@
         <v>241</v>
       </c>
       <c r="B13" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
@@ -1730,7 +1727,7 @@
         <v>242</v>
       </c>
       <c r="B18" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -1746,7 +1743,7 @@
         <v>243</v>
       </c>
       <c r="B20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -1770,7 +1767,7 @@
         <v>244</v>
       </c>
       <c r="B23" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -1802,7 +1799,7 @@
         <v>246</v>
       </c>
       <c r="B27" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -1810,7 +1807,7 @@
         <v>247</v>
       </c>
       <c r="B28" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -1842,7 +1839,7 @@
         <v>249</v>
       </c>
       <c r="B32" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -1882,7 +1879,7 @@
         <v>250</v>
       </c>
       <c r="B37" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -1890,7 +1887,7 @@
         <v>251</v>
       </c>
       <c r="B38" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -1906,7 +1903,7 @@
         <v>252</v>
       </c>
       <c r="B40" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -1946,7 +1943,7 @@
         <v>245</v>
       </c>
       <c r="B45" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
@@ -1962,7 +1959,7 @@
         <v>248</v>
       </c>
       <c r="B47" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
@@ -2079,7 +2076,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B62" t="s">
         <v>66</v>
@@ -2087,7 +2084,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B63" t="s">
         <v>67</v>
@@ -2095,7 +2092,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B64" t="s">
         <v>68</v>
@@ -2103,7 +2100,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B65" t="s">
         <v>69</v>
@@ -2122,7 +2119,7 @@
         <v>253</v>
       </c>
       <c r="B67" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
@@ -2202,7 +2199,7 @@
         <v>256</v>
       </c>
       <c r="B77" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
@@ -2258,7 +2255,7 @@
         <v>258</v>
       </c>
       <c r="B84" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
@@ -2287,26 +2284,26 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B88" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B89" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B90" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
@@ -2319,10 +2316,10 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B92" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
@@ -2335,18 +2332,18 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B94" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B95" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
@@ -2383,10 +2380,10 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B100" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
@@ -2455,10 +2452,10 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B109" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
@@ -2495,7 +2492,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B114" t="s">
         <v>123</v>
@@ -2503,10 +2500,10 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B115" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
@@ -2527,10 +2524,10 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B118" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
@@ -2551,10 +2548,10 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B121" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
@@ -2631,10 +2628,10 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B131" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
@@ -2647,7 +2644,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>363</v>
+        <v>148</v>
       </c>
       <c r="B133" t="s">
         <v>148</v>
@@ -2679,15 +2676,15 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B137" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B138" t="s">
         <v>155</v>
@@ -2695,15 +2692,15 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B139" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B140" t="s">
         <v>156</v>
@@ -2711,18 +2708,18 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B141" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B142" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
@@ -2735,10 +2732,10 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B144" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
@@ -2751,10 +2748,10 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B146" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
@@ -2767,10 +2764,10 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B148" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
@@ -2783,10 +2780,10 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B150" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
@@ -2815,10 +2812,10 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B154" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
@@ -2863,26 +2860,26 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B160" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B161" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B162" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
@@ -2895,18 +2892,18 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B164" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B165" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
@@ -2919,18 +2916,18 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B167" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B168" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
@@ -2983,10 +2980,10 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B175" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
@@ -3007,10 +3004,10 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B178" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
@@ -3023,10 +3020,10 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B180" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
@@ -3071,26 +3068,26 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B186" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B187" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B188" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
@@ -3103,10 +3100,10 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B190" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
@@ -3127,18 +3124,18 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B193" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B194" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
@@ -3151,18 +3148,18 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B196" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B197" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
@@ -3183,10 +3180,10 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B200" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
@@ -3207,18 +3204,18 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B203" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>291</v>
+        <v>373</v>
       </c>
       <c r="B204" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
@@ -3239,18 +3236,18 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B207" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B208" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
@@ -3335,10 +3332,10 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B219" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
@@ -3351,18 +3348,18 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B221" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B222" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
@@ -3383,10 +3380,10 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B225" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
@@ -3399,18 +3396,18 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B227" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>259</v>
+        <v>372</v>
       </c>
       <c r="B228" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
